--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -810,7 +810,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -996,7 +996,7 @@
 Executer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -794,7 +794,7 @@
     <t>Used to identify the thing to be done.</t>
   </si>
   <si>
-    <t>1845: reference from PRESCRIPTION REFILL REQUEST - Rx# (52.43-3)</t>
+    <t>1845: reference from PRESCRIPTION REFILL REQUEST - RX # (52.43-3)</t>
   </si>
   <si>
     <t>RxOut.RefillRequest.RxNumber</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -778,7 +778,7 @@
     <t>Task.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/MedicationDispenseRefill)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -747,7 +747,7 @@
     <t>http://hl7.org/fhir/ValueSet/task-code</t>
   </si>
   <si>
-    <t>1861: fixed value = FF case 31 RELEASED DATE/TIME null (never filled)</t>
+    <t>1861: fixed value = #FF case 31 RELEASED DATE/TIME null (never filled)</t>
   </si>
   <si>
     <t>Request.code, Event.code</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -604,7 +604,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFRefillRequestStatus</t>
+    <t>http://va.gov/fhir/ValueSet/RefillRequestStatus</t>
   </si>
   <si>
     <t>1848: terminologyMaps using VF_RefillRequestStatus on PRESCRIPTION REFILL REQUEST - RESULT (52.43-6)</t>
@@ -1730,7 +1730,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.1328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.60546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2203" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2203" uniqueCount="442">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -745,6 +745,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/task-code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+MedRefillRequestMHVTask-1852:if 31 RELEASED DATE/TIME not null (filled at least once) then fixed value #RF {null}MedRefillRequestMHVTask-1861:if 31 RELEASED DATE/TIME null (never filled) then fixed value #FF {null}</t>
   </si>
   <si>
     <t>1861: fixed value = #FF case 31 RELEASED DATE/TIME null (never filled)</t>
@@ -4371,22 +4375,22 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>236</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -4394,10 +4398,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4420,13 +4424,13 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4477,7 +4481,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4501,7 +4505,7 @@
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4512,10 +4516,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4538,19 +4542,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4599,7 +4603,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4614,19 +4618,19 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
@@ -4634,14 +4638,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4660,17 +4664,17 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4719,7 +4723,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4734,19 +4738,19 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>79</v>
@@ -4754,10 +4758,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4780,17 +4784,17 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4839,7 +4843,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4860,13 +4864,13 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -4874,10 +4878,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4900,13 +4904,13 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4957,7 +4961,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4978,13 +4982,13 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -4992,14 +4996,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5018,17 +5022,17 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5077,7 +5081,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5086,7 +5090,7 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>101</v>
@@ -5098,13 +5102,13 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5112,14 +5116,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5138,17 +5142,17 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5197,7 +5201,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5206,7 +5210,7 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>101</v>
@@ -5221,7 +5225,7 @@
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5232,10 +5236,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5258,17 +5262,17 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5317,7 +5321,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5338,13 +5342,13 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -5352,10 +5356,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5381,14 +5385,14 @@
         <v>196</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5416,10 +5420,10 @@
         <v>113</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5437,7 +5441,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5458,13 +5462,13 @@
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -5472,14 +5476,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5498,19 +5502,19 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5559,7 +5563,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5574,19 +5578,19 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -5594,10 +5598,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5620,17 +5624,17 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5679,7 +5683,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5700,13 +5704,13 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -5714,10 +5718,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5743,13 +5747,13 @@
         <v>196</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5778,7 +5782,7 @@
         <v>200</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>79</v>
@@ -5799,7 +5803,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5820,24 +5824,24 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5863,13 +5867,13 @@
         <v>165</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5919,7 +5923,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5940,13 +5944,13 @@
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -5954,10 +5958,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5980,13 +5984,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6037,7 +6041,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6058,24 +6062,24 @@
         <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6098,13 +6102,13 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6155,7 +6159,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6170,16 +6174,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6190,14 +6194,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6216,16 +6220,16 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6275,7 +6279,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6296,10 +6300,10 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6310,10 +6314,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6336,17 +6340,17 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6395,7 +6399,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6419,7 +6423,7 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6430,10 +6434,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6456,13 +6460,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6513,7 +6517,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6537,7 +6541,7 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6548,10 +6552,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6580,7 +6584,7 @@
         <v>136</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>138</v>
@@ -6633,7 +6637,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6657,7 +6661,7 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6668,14 +6672,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6697,10 +6701,10 @@
         <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>138</v>
@@ -6755,7 +6759,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6790,10 +6794,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6816,17 +6820,17 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6875,7 +6879,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6899,7 +6903,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -6910,10 +6914,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6936,19 +6940,19 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6997,7 +7001,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7021,7 +7025,7 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7032,10 +7036,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7058,13 +7062,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7115,7 +7119,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7139,7 +7143,7 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7150,14 +7154,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7176,17 +7180,17 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7235,7 +7239,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7259,7 +7263,7 @@
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7270,10 +7274,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7296,13 +7300,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7353,7 +7357,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7377,7 +7381,7 @@
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7388,10 +7392,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7420,7 +7424,7 @@
         <v>136</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>138</v>
@@ -7473,7 +7477,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7497,7 +7501,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7508,14 +7512,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7537,10 +7541,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>138</v>
@@ -7595,7 +7599,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7630,14 +7634,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7659,16 +7663,16 @@
         <v>196</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7696,7 +7700,7 @@
         <v>200</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>79</v>
@@ -7717,7 +7721,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>89</v>
@@ -7741,7 +7745,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7752,10 +7756,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7778,13 +7782,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7835,7 +7839,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -7859,7 +7863,7 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7870,10 +7874,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7896,17 +7900,17 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7955,7 +7959,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7979,7 +7983,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -7990,10 +7994,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8016,13 +8020,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8073,7 +8077,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8097,7 +8101,7 @@
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8108,10 +8112,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8140,7 +8144,7 @@
         <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>138</v>
@@ -8193,7 +8197,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8217,7 +8221,7 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8228,14 +8232,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8257,10 +8261,10 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>138</v>
@@ -8315,7 +8319,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8350,14 +8354,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8379,14 +8383,14 @@
         <v>196</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8414,7 +8418,7 @@
         <v>200</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>79</v>
@@ -8435,7 +8439,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>89</v>
@@ -8459,7 +8463,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8470,10 +8474,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8496,17 +8500,17 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8555,7 +8559,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>89</v>
@@ -8579,7 +8583,7 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -748,7 +748,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-MedRefillRequestMHVTask-1852:if 31 RELEASED DATE/TIME not null (filled at least once) then fixed value #RF {null}MedRefillRequestMHVTask-1861:if 31 RELEASED DATE/TIME null (never filled) then fixed value #FF {null}</t>
+mrrmhvt-23-1852:null: if 31 RELEASED DATE/TIME not null (filled at least once) then #RF {null}mrrmhvt-23-1861:null: if 31 RELEASED DATE/TIME null (never filled) then #FF {null}</t>
   </si>
   <si>
     <t>1861: fixed value = #FF case 31 RELEASED DATE/TIME null (never filled)</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION REFILL REQUEST (52.43) to Task</t>
+    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION REFILL REQUEST (52.43) to Task.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -748,10 +748,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mrrmhvt-23-1852:null: if 31 RELEASED DATE/TIME not null (filled at least once) then #RF {null}mrrmhvt-23-1861:null: if 31 RELEASED DATE/TIME null (never filled) then #FF {null}</t>
-  </si>
-  <si>
-    <t>1861: fixed value = #FF case 31 RELEASED DATE/TIME null (never filled)</t>
+mrrmhvt-23-1852:If (null) is 31 RELEASED DATE/TIME not null (filled at least once) then fixed value #RF {null}mrrmhvt-23-1861:If (null) is 31 RELEASED DATE/TIME null (never filled) then fixed value #FF {null}</t>
+  </si>
+  <si>
+    <t>1861: fixed value = #FF if 31 RELEASED DATE/TIME null (never filled)</t>
   </si>
   <si>
     <t>Request.code, Event.code</t>
@@ -798,7 +798,7 @@
     <t>Used to identify the thing to be done.</t>
   </si>
   <si>
-    <t>1845: reference from PRESCRIPTION REFILL REQUEST - RX # (52.43-3)</t>
+    <t>1845: reference based on PRESCRIPTION REFILL REQUEST - RX # (52.43-3)</t>
   </si>
   <si>
     <t>RxOut.RefillRequest.RxNumber</t>
@@ -827,7 +827,7 @@
     <t>Used to track tasks outstanding for a beneficiary.  Do not use to track the task owner or creator (see owner and creator respectively).  This can also affect access control.</t>
   </si>
   <si>
-    <t>1844: reference from PRESCRIPTION REFILL REQUEST - PATIENT (52.43-9)</t>
+    <t>1844: reference based on PRESCRIPTION REFILL REQUEST - PATIENT (52.43-9)</t>
   </si>
   <si>
     <t>RxOut.RefillRequest.PatientIEN</t>
@@ -1016,7 +1016,7 @@
     <t>Identifies who is expected to perform this task.</t>
   </si>
   <si>
-    <t>1846: reference from PRESCRIPTION REFILL REQUEST - INSTITUTION (52.43-4)</t>
+    <t>1846: reference based on PRESCRIPTION REFILL REQUEST - INSTITUTION (52.43-4)</t>
   </si>
   <si>
     <t>RxOut.RefillRequest.InstitutionCode</t>
@@ -1130,7 +1130,7 @@
     <t>Free-text information captured about the task as it progresses.</t>
   </si>
   <si>
-    <t>1849: source value from PRESCRIPTION REFILL REQUEST - REMARKS (52.43-10)</t>
+    <t>1849: source value based on PRESCRIPTION REFILL REQUEST - REMARKS (52.43-10)</t>
   </si>
   <si>
     <t>RxOut.RefillRequest.RefillRequestRemarks</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2203" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="443">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -602,6 +602,9 @@
   </si>
   <si>
     <t>required</t>
+  </si>
+  <si>
+    <t>see mapping [VF_RefillRequestStatus](ConceptMap-VF-RefillRequestStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/RefillRequestStatus</t>
@@ -3741,9 +3744,11 @@
       <c r="X17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y17" s="2"/>
+      <c r="Y17" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3776,19 +3781,19 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>79</v>
@@ -3796,10 +3801,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3822,16 +3827,16 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3857,10 +3862,10 @@
         <v>79</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z18" t="s" s="2">
         <v>79</v>
@@ -3881,7 +3886,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3905,7 +3910,7 @@
         <v>79</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>79</v>
@@ -3916,10 +3921,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3942,17 +3947,17 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>79</v>
@@ -3977,10 +3982,10 @@
         <v>79</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Z19" t="s" s="2">
         <v>79</v>
@@ -4001,7 +4006,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4025,7 +4030,7 @@
         <v>79</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>79</v>
@@ -4036,10 +4041,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4065,13 +4070,13 @@
         <v>109</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4082,7 +4087,7 @@
         <v>79</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>79</v>
@@ -4100,10 +4105,10 @@
         <v>188</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>79</v>
@@ -4121,7 +4126,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4136,19 +4141,19 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -4156,10 +4161,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4185,20 +4190,20 @@
         <v>109</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q21" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="R21" t="s" s="2">
         <v>79</v>
@@ -4222,10 +4227,10 @@
         <v>188</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>79</v>
@@ -4243,7 +4248,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4264,13 +4269,13 @@
         <v>79</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -4278,10 +4283,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4304,16 +4309,16 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4339,13 +4344,13 @@
         <v>79</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>79</v>
@@ -4363,7 +4368,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4375,22 +4380,22 @@
         <v>79</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -4398,10 +4403,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4424,13 +4429,13 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4481,7 +4486,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4505,7 +4510,7 @@
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>79</v>
@@ -4516,10 +4521,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4542,19 +4547,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4603,7 +4608,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4618,19 +4623,19 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
@@ -4638,14 +4643,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4664,17 +4669,17 @@
         <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>79</v>
@@ -4723,7 +4728,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4738,19 +4743,19 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>79</v>
@@ -4758,10 +4763,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4784,17 +4789,17 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>79</v>
@@ -4843,7 +4848,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4864,13 +4869,13 @@
         <v>79</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>79</v>
@@ -4878,10 +4883,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4904,13 +4909,13 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4961,7 +4966,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4982,13 +4987,13 @@
         <v>79</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>79</v>
@@ -4996,14 +5001,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5022,17 +5027,17 @@
         <v>79</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>79</v>
@@ -5081,7 +5086,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5090,7 +5095,7 @@
         <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>101</v>
@@ -5102,13 +5107,13 @@
         <v>79</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>79</v>
@@ -5116,14 +5121,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5142,17 +5147,17 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>79</v>
@@ -5201,7 +5206,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5210,7 +5215,7 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>101</v>
@@ -5225,7 +5230,7 @@
         <v>79</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -5236,10 +5241,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5262,17 +5267,17 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>79</v>
@@ -5321,7 +5326,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5342,13 +5347,13 @@
         <v>79</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>79</v>
@@ -5356,10 +5361,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5382,17 +5387,17 @@
         <v>79</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>79</v>
@@ -5420,10 +5425,10 @@
         <v>113</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
@@ -5441,7 +5446,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5462,13 +5467,13 @@
         <v>79</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>79</v>
@@ -5476,14 +5481,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5502,19 +5507,19 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5563,7 +5568,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5578,19 +5583,19 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>79</v>
@@ -5598,10 +5603,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5624,17 +5629,17 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
@@ -5683,7 +5688,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5704,13 +5709,13 @@
         <v>79</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>79</v>
@@ -5718,10 +5723,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5744,16 +5749,16 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5779,10 +5784,10 @@
         <v>79</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>79</v>
@@ -5803,7 +5808,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5824,24 +5829,24 @@
         <v>79</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5867,13 +5872,13 @@
         <v>165</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5923,7 +5928,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5944,13 +5949,13 @@
         <v>79</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>79</v>
@@ -5958,10 +5963,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5984,13 +5989,13 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6041,7 +6046,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6062,24 +6067,24 @@
         <v>79</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6102,13 +6107,13 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6159,7 +6164,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6174,16 +6179,16 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -6194,14 +6199,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6220,16 +6225,16 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6279,7 +6284,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6300,10 +6305,10 @@
         <v>79</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>
@@ -6314,10 +6319,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6340,17 +6345,17 @@
         <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6399,7 +6404,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6423,7 +6428,7 @@
         <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>79</v>
@@ -6434,10 +6439,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6460,13 +6465,13 @@
         <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6517,7 +6522,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6541,7 +6546,7 @@
         <v>79</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>79</v>
@@ -6552,10 +6557,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6584,7 +6589,7 @@
         <v>136</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>138</v>
@@ -6637,7 +6642,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6661,7 +6666,7 @@
         <v>79</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>79</v>
@@ -6672,14 +6677,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6701,10 +6706,10 @@
         <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>138</v>
@@ -6759,7 +6764,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6794,10 +6799,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6820,17 +6825,17 @@
         <v>79</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
@@ -6879,7 +6884,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6903,7 +6908,7 @@
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -6914,10 +6919,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6940,19 +6945,19 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -7001,7 +7006,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7025,7 +7030,7 @@
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -7036,10 +7041,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7062,13 +7067,13 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7119,7 +7124,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7143,7 +7148,7 @@
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>79</v>
@@ -7154,14 +7159,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7180,17 +7185,17 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7239,7 +7244,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7263,7 +7268,7 @@
         <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>79</v>
@@ -7274,10 +7279,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7300,13 +7305,13 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7357,7 +7362,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7381,7 +7386,7 @@
         <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>79</v>
@@ -7392,10 +7397,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7424,7 +7429,7 @@
         <v>136</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>138</v>
@@ -7477,7 +7482,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7501,7 +7506,7 @@
         <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>79</v>
@@ -7512,14 +7517,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7541,10 +7546,10 @@
         <v>135</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>138</v>
@@ -7599,7 +7604,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7634,14 +7639,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7660,19 +7665,19 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7697,10 +7702,10 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z50" t="s" s="2">
         <v>79</v>
@@ -7721,7 +7726,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>89</v>
@@ -7745,7 +7750,7 @@
         <v>79</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>79</v>
@@ -7756,10 +7761,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7782,13 +7787,13 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7839,7 +7844,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>89</v>
@@ -7863,7 +7868,7 @@
         <v>79</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>79</v>
@@ -7874,10 +7879,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7900,17 +7905,17 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7959,7 +7964,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7983,7 +7988,7 @@
         <v>79</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>79</v>
@@ -7994,10 +7999,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8020,13 +8025,13 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8077,7 +8082,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8101,7 +8106,7 @@
         <v>79</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>79</v>
@@ -8112,10 +8117,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8144,7 +8149,7 @@
         <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>138</v>
@@ -8197,7 +8202,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8221,7 +8226,7 @@
         <v>79</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>79</v>
@@ -8232,14 +8237,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8261,10 +8266,10 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>138</v>
@@ -8319,7 +8324,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8354,14 +8359,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8380,17 +8385,17 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
@@ -8415,10 +8420,10 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>79</v>
@@ -8439,7 +8444,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>89</v>
@@ -8463,7 +8468,7 @@
         <v>79</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>79</v>
@@ -8474,10 +8479,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8500,17 +8505,17 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8559,7 +8564,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>89</v>
@@ -8583,7 +8588,7 @@
         <v>79</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>79</v>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -751,10 +751,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-mrrmhvt-23-1852:If (null) is 31 RELEASED DATE/TIME not null (filled at least once) then fixed value #RF {null}mrrmhvt-23-1861:If (null) is 31 RELEASED DATE/TIME null (never filled) then fixed value #FF {null}</t>
-  </si>
-  <si>
-    <t>1861: fixed value = #FF if 31 RELEASED DATE/TIME null (never filled)</t>
+mrrmhvt-23-1852:If 31 RELEASED DATE/TIME not null then fixed value #RF {true}mrrmhvt-23-1861:If 31 RELEASED DATE/TIME null then fixed value #FF {true}</t>
+  </si>
+  <si>
+    <t>1861: fixed value = #FF if 31 RELEASED DATE/TIME null</t>
   </si>
   <si>
     <t>Request.code, Event.code</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
+++ b/docs/StructureDefinition-MedRefillRequestMHVTask.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
